--- a/tools/levels/out/台面配置表.xlsx
+++ b/tools/levels/out/台面配置表.xlsx
@@ -55,7 +55,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78,664; 282,664</t>
+          <t xml:space="preserve">113,743; 279,839</t>
         </is>
       </c>
     </row>
@@ -70,9 +70,9 @@
           <t xml:space="preserve">三角柱</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78,640; 282,640; 124,688; 236,688; 78,736; 282,736</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330,603,330,723,rubber</t>
         </is>
       </c>
     </row>
@@ -87,14 +87,9 @@
           <t xml:space="preserve">彈力牆</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96,664; 264,664</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23,610,23,730,rubber; 337,610,337,730,rubber</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284,745; 284,744; 55,846</t>
         </is>
       </c>
     </row>
@@ -349,6 +344,45 @@
       <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">82,773; 222,773</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a_fish_4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阿鰭（第 4 關）</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31,756,31,876,rubber; 329,750,329,870,rubber</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153,692</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c_fish_5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阿鰭（第 5 關）</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738,20,340,110</t>
         </is>
       </c>
     </row>

--- a/tools/levels/out/台面配置表.xlsx
+++ b/tools/levels/out/台面配置表.xlsx
@@ -53,11 +53,6 @@
           <t xml:space="preserve">雙柱</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113,743; 279,839</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
